--- a/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élodie est dans la cuisine. Papa est là. Une petite menthe a soif. Ses feuilles sont molles. Papa dit : elle a besoin d'eau. Elle a besoin de lumière. Élodie prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Élodie touche une feuille. C'est doux. Ça sent la menthe. Papa dit : on arrose avec un adulte. Élodie répète : eau, lumière, adulte. La menthe tient plus droit.</t>
+          <t>Élodie est dans la cuisine. Papa est là. Une petite menthe a soif. Ses feuilles sont molles. Elle a besoin d'eau. Elle a besoin de lumière. Élodie prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Élodie touche une feuille. C'est doux. Ça sent la menthe. On arrose avec un adulte. Élodie répète : eau, lumière, adulte. La menthe tient plus droit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Élodie est dans la cuisine. Papa est là. Une petite menthe a soif. Ses feuilles sont molles.
+papa|Elle a besoin d'eau. Elle a besoin de lumière.
+narrateur|Élodie prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Élodie touche une feuille. C'est doux. Ça sent la menthe.
+papa|On arrose avec un adulte.
+narrateur|Élodie répète : eau, lumière, adulte. La menthe tient plus droit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a soif. Que fait Élodie avec papa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Élodie a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Élodie range l'arrosoir. La menthe tient droit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Élodie répète : eau, lumière, adulte. La menthe tient plus droit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|La plante a soif. Que fait Élodie avec papa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Élodie a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Élodie range l'arrosoir. La menthe tient droit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Élodie arrose la menthe</t>
+          <t>Le thé de menthe de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut du thé à la menthe. Une vieille feuille est amère. Ils en cueillent une jeune. Ils arrosent. Le thé sent bon.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élodie est dans la cuisine. Papa est là. Une petite menthe a soif. Ses feuilles sont molles. Elle a besoin d'eau. Elle a besoin de lumière. Élodie prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Élodie touche une feuille. C'est doux. Ça sent la menthe. On arrose avec un adulte. Élodie répète : eau, lumière, adulte. La menthe tient plus droit.</t>
+          <t>La bouilloire fait un petit chant. Une vapeur colle au carreau. Le carreau devient un peu flou. Un pot de menthe attend au rebord. Les tiges sont minces. Quelques feuilles sont sombres. Papa pose deux tasses. Les tasses sont déjà un peu chaudes. Tu sens la menthe, Mila ? Oui, papa. Je veux du thé. On fait du thé, alors. En ce moment, Mila cueille une feuille. Cette feuille est sombre. Elle est un peu sèche. Je la mets dans l'eau ? Goûte d'abord, tout doux. Mila pose la feuille sur sa langue. C'est amer, papa. Cette feuille est trop vieille. On cherche une jeune feuille ? Oui. Papa penche le pot vers le jour. Une petite feuille brille au milieu. Elle est bien verte. Celle-là ? Oui, celle-là est jeune. Mila la cueille tout doux. Le pot penche un peu. La terre est trop sèche. La menthe a besoin d'eau. Elle a besoin de lumière. On arrose ? Oui, avec moi. Mila tient l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pousse le pot. Le jour arrive sur les feuilles. Elle tient plus droit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Élodie est dans la cuisine. Papa est là. Une petite menthe a soif. Ses feuilles sont molles. Papa dit : elle a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Élodie prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Élodie touche une feuille. C'est doux. Ça sent la menthe. Papa dit : on arrose avec un adulte. Élodie répète : eau, lumière, adulte. La menthe tient plus droit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire fait un petit chant. Une vapeur colle au carreau. Le carreau devient un peu flou. Un pot de menthe attend au rebord. Les tiges sont minces. Quelques feuilles sont sombres. Papa pose deux tasses. Les tasses sont déjà un peu chaudes. Tu sens la menthe, Mila ? Oui, papa. Je veux du thé. On fait du thé, alors. En ce moment, Mila cueille une feuille. Cette feuille est sombre. Elle est un peu sèche. Je la mets dans l'eau ? Goûte d'abord, tout doux. Mila pose la feuille sur sa langue. C'est amer, papa. Cette feuille est trop vieille. On cherche une jeune feuille ? Oui. Papa penche le pot vers le jour. Une petite feuille brille au milieu. Elle est bien verte. Celle-là ? Oui, celle-là est jeune. Mila la cueille tout doux. Le pot penche un peu. La terre est trop sèche. La menthe a besoin d'eau. Elle a besoin de lumière. On arrose ? Oui, avec moi. Mila tient l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pousse le pot. Le jour arrive sur les feuilles. Elle tient plus droit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Élodie est dans la cuisine. Papa est là. Une petite menthe a soif. Ses feuilles sont molles.
-papa|Elle a besoin d'eau. Elle a besoin de lumière.
-narrateur|Élodie prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Élodie touche une feuille. C'est doux. Ça sent la menthe.
-papa|On arrose avec un adulte.
-narrateur|Élodie répète : eau, lumière, adulte. La menthe tient plus droit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La bouilloire fait un petit chant.
+narrateur|Une vapeur colle au carreau.
+narrateur|Le carreau devient un peu flou.
+narrateur|Un pot de menthe attend au rebord.
+narrateur|Les tiges sont minces.
+narrateur|Quelques feuilles sont sombres.
+narrateur|Papa pose deux tasses.
+narrateur|Les tasses sont déjà un peu chaudes.
+papa|Tu sens la menthe, Mila ?
+enfant-f|Oui, papa.
+enfant-f|Je veux du thé.
+papa|On fait du thé, alors.
+narrateur|En ce moment, Mila cueille une feuille.
+narrateur|Cette feuille est sombre.
+narrateur|Elle est un peu sèche.
+enfant-f|Je la mets dans l'eau ?
+papa|Goûte d'abord, tout doux.
+narrateur|Mila pose la feuille sur sa langue.
+enfant-f|C'est amer, papa.
+papa|Cette feuille est trop vieille.
+papa|On cherche une jeune feuille ?
+enfant-f|Oui.
+narrateur|Papa penche le pot vers le jour.
+narrateur|Une petite feuille brille au milieu.
+narrateur|Elle est bien verte.
+enfant-f|Celle-là ?
+papa|Oui, celle-là est jeune.
+narrateur|Mila la cueille tout doux.
+narrateur|Le pot penche un peu.
+papa|La terre est trop sèche.
+papa|La menthe a besoin d'eau.
+papa|Elle a besoin de lumière.
+enfant-f|On arrose ?
+papa|Oui, avec moi.
+narrateur|Mila tient l'arrosoir avec papa.
+narrateur|Ils versent un peu d'eau.
+narrateur|La terre devient sombre.
+narrateur|Papa pousse le pot.
+narrateur|Le jour arrive sur les feuilles.
+enfant-f|Elle tient plus droit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1390,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La plante a soif. Que fait Élodie avec papa ?</t>
+          <t>La menthe a soif. Que fait Mila avec papa ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La plante a soif. Que fait Élodie avec papa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La menthe a soif. Que fait Mila avec papa ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1410,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>arroser | elle arrose | de l'eau | eau</t>
+          <t>arroser | de l'eau | eau | lumière | avec papa</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils versent de l'eau. Que fait Élodie ?</t>
+          <t>Ils versent de l'eau. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1474,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1546,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La plante a soif. Que fait Élodie avec papa ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La menthe a soif.
+narrateur|Que fait Mila avec papa ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Élodie a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
+          <t>Mila pose la jeune feuille dans la tasse. Papa verse l'eau tout doux. La vapeur sent tout de suite la menthe. Ça sent bon. Ce n'est plus amer. Merci, Mila. Ils soufflent un peu. L'eau est encore chaude. On attend un peu ? Oui, papa. Mila regarde le pot au rebord. Les jeunes feuilles brillent. Elle a de l'eau. Et de la lumière. Une goutte reste sur la terre. Mila ne la touche pas. La tasse est prête ? Presque. Mila souffle encore un peu. La vapeur danse au-dessus de l'eau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Élodie a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Papa, l'adulte, était avec elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila pose la jeune feuille dans la tasse. Papa verse l'eau tout doux. La vapeur sent tout de suite la menthe. Ça sent bon. Ce n'est plus amer. Merci, Mila. Ils soufflent un peu. L'eau est encore chaude. On attend un peu ? Oui, papa. Mila regarde le pot au rebord. Les jeunes feuilles brillent. Elle a de l'eau. Et de la lumière. Une goutte reste sur la terre. Mila ne la touche pas. La tasse est prête ? Presque. Mila souffle encore un peu. La vapeur danse au-dessus de l'eau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1589,14 +1635,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1718,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Élodie a versé l'eau. La lumière est là. Papa, l'adulte, était avec elle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila pose la jeune feuille dans la tasse.
+narrateur|Papa verse l'eau tout doux.
+narrateur|La vapeur sent tout de suite la menthe.
+enfant-f|Ça sent bon.
+papa|Ce n'est plus amer.
+papa|Merci, Mila.
+narrateur|Ils soufflent un peu.
+narrateur|L'eau est encore chaude.
+papa|On attend un peu ?
+enfant-f|Oui, papa.
+narrateur|Mila regarde le pot au rebord.
+narrateur|Les jeunes feuilles brillent.
+enfant-f|Elle a de l'eau.
+papa|Et de la lumière.
+narrateur|Une goutte reste sur la terre.
+narrateur|Mila ne la touche pas.
+papa|La tasse est prête ?
+enfant-f|Presque.
+narrateur|Mila souffle encore un peu.
+narrateur|La vapeur danse au-dessus de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Élodie range l'arrosoir. La menthe tient droit.</t>
+          <t>Mila goûte le thé. Ce n'est pas amer. C'est la jeune feuille. La tasse chauffe ses mains. Papa goûte aussi. Ça sent la menthe. Oui. Le carreau n'est plus flou. La vapeur est partie. On range l'arrosoir ? Oui, papa. Mila pose l'arrosoir près du mur. Le métal est encore un peu mouillé. La menthe a de l'eau. Oui, et de la lumière.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Élodie range l'arrosoir. La menthe tient droit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila goûte le thé. Ce n'est pas amer. C'est la jeune feuille. La tasse chauffe ses mains. Papa goûte aussi. Ça sent la menthe. Oui. Le carreau n'est plus flou. La vapeur est partie. On range l'arrosoir ? Oui, papa. Mila pose l'arrosoir près du mur. Le métal est encore un peu mouillé. La menthe a de l'eau. Oui, et de la lumière.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1761,14 +1825,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1900,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Élodie range l'arrosoir. La menthe tient droit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila goûte le thé.
+enfant-f|Ce n'est pas amer.
+papa|C'est la jeune feuille.
+narrateur|La tasse chauffe ses mains.
+narrateur|Papa goûte aussi.
+papa|Ça sent la menthe.
+enfant-f|Oui.
+narrateur|Le carreau n'est plus flou.
+narrateur|La vapeur est partie.
+papa|On range l'arrosoir ?
+enfant-f|Oui, papa.
+narrateur|Mila pose l'arrosoir près du mur.
+narrateur|Le métal est encore un peu mouillé.
+enfant-f|La menthe a de l'eau.
+papa|Oui, et de la lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le thé sent encore la menthe. La jeune feuille est dedans. Oui. Le pot tient droit au rebord. Le jour reste sur les feuilles.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le thé sent encore la menthe. La jeune feuille est dedans. Oui. Le pot tient droit au rebord. Le jour reste sur les feuilles.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2002,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2081,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le thé sent encore la menthe.
+enfant-f|La jeune feuille est dedans.
+papa|Oui.
+narrateur|Le pot tient droit au rebord.
+narrateur|Le jour reste sur les feuilles.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Élodie, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
